--- a/ds_0120.xlsx
+++ b/ds_0120.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\งานดาต้า\ข้อมูลขึ้น Github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783E72F5-5C5F-4264-B424-326DB8389F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AFF288-3606-4484-8C4B-D3F5B7B9B719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="26325" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
@@ -383,9 +383,6 @@
     <t>อว 0652.14</t>
   </si>
   <si>
-    <t>สถาบันสหวิทยากรดิจิทัลและหุ่นยนต์</t>
-  </si>
-  <si>
     <t>Institute of Digital Interdisciplinary Experts and Robotics</t>
   </si>
   <si>
@@ -544,6 +541,9 @@
   </si>
   <si>
     <t>หน่วยตรวจสอบภายใน</t>
+  </si>
+  <si>
+    <t>สถาบันสหวิทยาการดิจิทัลและหุ่นยนต์</t>
   </si>
 </sst>
 </file>
@@ -933,7 +933,7 @@
     <col min="2" max="2" width="39.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="14.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -941,7 +941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="14.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -949,7 +949,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" ht="28.5">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -957,7 +957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="14.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -973,15 +973,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="14.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -989,7 +989,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" ht="28.5">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -997,7 +997,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" ht="14.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" ht="28.5">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" ht="28.5">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" ht="28.5">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" ht="14.25">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" ht="14.25">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" ht="28.5">
       <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" ht="14.25">
       <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" ht="14.25">
       <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" ht="28.5">
       <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
@@ -1077,12 +1077,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" ht="14.25">
       <c r="A19" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B19" s="5">
-        <v>46161</v>
+        <v>46308</v>
       </c>
     </row>
   </sheetData>
@@ -4261,7 +4261,8 @@
     <col min="1" max="1" width="7.28515625" customWidth="1"/>
     <col min="3" max="3" width="38.5703125" customWidth="1"/>
     <col min="4" max="4" width="51.5703125" customWidth="1"/>
-    <col min="5" max="7" width="30.42578125" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" customWidth="1"/>
+    <col min="6" max="7" width="30.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="12.75">
@@ -4617,16 +4618,16 @@
         <v>15</v>
       </c>
       <c r="C16" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="E16" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="F16" s="12" t="s">
         <v>119</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>120</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>63</v>
@@ -4640,16 +4641,16 @@
         <v>16</v>
       </c>
       <c r="C17" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="E17" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="F17" s="12" t="s">
         <v>122</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>123</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>63</v>
@@ -4663,16 +4664,16 @@
         <v>17</v>
       </c>
       <c r="C18" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="E18" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="F18" s="12" t="s">
         <v>126</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>127</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>63</v>
@@ -4686,16 +4687,16 @@
         <v>18</v>
       </c>
       <c r="C19" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="E19" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="F19" s="12" t="s">
         <v>130</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>131</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>63</v>
@@ -4709,16 +4710,16 @@
         <v>19</v>
       </c>
       <c r="C20" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="E20" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="F20" s="12" t="s">
         <v>134</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>135</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>63</v>
@@ -4732,16 +4733,16 @@
         <v>20</v>
       </c>
       <c r="C21" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="E21" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="F21" s="12" t="s">
         <v>138</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>139</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>63</v>
@@ -4755,16 +4756,16 @@
         <v>21</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D22" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="E22" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="F22" s="12" t="s">
         <v>141</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>142</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>63</v>
@@ -4778,16 +4779,16 @@
         <v>22</v>
       </c>
       <c r="C23" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D23" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="E23" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="F23" s="12" t="s">
         <v>166</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>167</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>63</v>
@@ -4801,16 +4802,16 @@
         <v>23</v>
       </c>
       <c r="C24" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="E24" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="F24" s="12" t="s">
         <v>145</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>146</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>63</v>
@@ -4824,16 +4825,16 @@
         <v>24</v>
       </c>
       <c r="C25" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="E25" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="F25" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>150</v>
       </c>
       <c r="G25" s="12" t="s">
         <v>68</v>
@@ -4847,16 +4848,16 @@
         <v>25</v>
       </c>
       <c r="C26" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="E26" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="F26" s="12" t="s">
         <v>153</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>154</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>63</v>
@@ -4870,16 +4871,16 @@
         <v>26</v>
       </c>
       <c r="C27" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="D27" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="E27" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="F27" s="12" t="s">
         <v>157</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>158</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>68</v>
@@ -4893,16 +4894,16 @@
         <v>27</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D28" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="F28" s="12" t="s">
         <v>160</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>161</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>63</v>
@@ -4916,19 +4917,19 @@
         <v>99</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
